--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260610.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>672,350,000</t>
+          <t>555,720,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.81%</t>
+          <t>12.67%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>535,870,000</t>
+          <t>669,730,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.27%</t>
+          <t>12.45%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>919,017,000</t>
+          <t>909,417,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.65%</t>
+          <t>11.54%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>123,100,000</t>
+          <t>144,330,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>8.46%</t>
+          <t>10.22%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,112,330,000</t>
+          <t>1,123,300,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.02%</t>
+          <t>6.04%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>35,830,000</t>
+          <t>35,060,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.19%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>104,423,000</t>
+          <t>102,213,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.24%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.67%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>146,022,000</t>
+          <t>684,320,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>590,960,000</t>
+          <t>19,350,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -836,73 +836,73 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>16,700,000</t>
+          <t>274,224,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>279,434,000</t>
+          <t>98,520,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>85,040,000</t>
+          <t>73,012,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>8,800,000</t>
+          <t>10,180,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -941,100 +941,100 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>52,700,000</t>
+          <t>61,090,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>27,970,000</t>
+          <t>72,239,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>72,239,000</t>
+          <t>26,910,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>56,760,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>49,040,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1051,34 +1051,34 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>156,740,000</t>
+          <t>181,870,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>10,514,000</t>
+          <t>10,478,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1100,112 +1100,112 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>42,230,000</t>
+          <t>10,014,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>7,580,000</t>
+          <t>103,540,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,600,000</t>
+          <t>64,550,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>11,610,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>89,440,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,418 +1217,418 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>55,740,000</t>
+          <t>39,730,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>57,950,000</t>
+          <t>66,150,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,274,000</t>
+          <t>38,943,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>2,336,000</t>
+          <t>24,560,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>38,943,000</t>
+          <t>27,720,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,816,000</t>
+          <t>27,549,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>16,280,000</t>
+          <t>12,530,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>27,779,000</t>
+          <t>26,440,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>15,212,441</t>
+          <t>15,950,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>57,220,000</t>
+          <t>7,770,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>21,200,000</t>
+          <t>36,530,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,770,000</t>
+          <t>26,666,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>26,666,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,820,000</t>
+          <t>19,910,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>22,331,000</t>
+          <t>6,290,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>22,840,000</t>
+          <t>28,990,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>4,654,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>19,910,000</t>
+          <t>1,176,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>31,540,000</t>
+          <t>7,602,441</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,199,000</t>
+          <t>2,599,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>11,040,000</t>
+          <t>5,520,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>10,771,000</t>
+          <t>5,381,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>17,940,000</t>
+          <t>8,980,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,820,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1755,56 +1755,56 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>10,020,000</t>
+          <t>4,990,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,530,000</t>
+          <t>1,710,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>3,410,000</t>
+          <t>2,250,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>6,700,000</t>
+          <t>3,330,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>6,816,000</t>
+          <t>3,396,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.02%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>6,980,000</t>
+          <t>3,470,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.02%</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>712,000</t>
+          <t>342,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.01%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>8,453,088,178</t>
+          <t>5,575,901,251</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>2,265,434,802</t>
+          <t>1,934,523,117</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>539,502,897</t>
+          <t>1,886,813,201</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
